--- a/Claude outputs/Mare_Durabilis_Budget_fonctionnement_2026_2029_ASSO_2.xlsx
+++ b/Claude outputs/Mare_Durabilis_Budget_fonctionnement_2026_2029_ASSO_2.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="499">
   <si>
     <t xml:space="preserve">ÉLIGIBILITÉ FEAMPA — RÈGLES GÉNÉRALES</t>
   </si>
@@ -934,7 +934,7 @@
     <t xml:space="preserve">Intérêts de l’avance de trésorerie du Crédit Maritime (non éligibles)</t>
   </si>
   <si>
-    <t xml:space="preserve">Repris de l'onglet Trésorerie (intérêts calculés trimestre par trimestre). 2029 inclut les intérêts courant en 2030 jusqu'au versement du solde FEAMPA. Non éligibles (intérêts débiteurs, art. 64 RPDC) : couverts par le fonds via le reste à charge.</t>
+    <t xml:space="preserve">Repris de l'onglet Trésorerie (intérêts calculés trimestre par trimestre). 2029 inclut les intérêts courant en 2030 et 2031 jusqu'au versement du solde FEAMPA. Non éligibles (intérêts débiteurs, art. 64 RPDC) : couverts par le fonds via le reste à charge.</t>
   </si>
   <si>
     <t xml:space="preserve">❌ Non éligible</t>
@@ -1294,7 +1294,7 @@
     <t xml:space="preserve">PLAN DE TRÉSORERIE DE L'ASSOCIATION — encaissements et décaissements par trimestre</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculé depuis les onglets Dépenses et Ressources. 2027 : charges et refacturations sur T3-T4 (recrutement au 1er juillet), formalités au T1 ; reste à charge (B.3) versé par quarts, comme au planning du fonds ; aide FEAMPA versée sur demande de paiement semestrielle, après service fait et sur factures acquittées. 2030 : seulement la fin de l'opération 2027-2029 (solde FEAMPA et remboursement de l'avance), sans les charges de 2030.</t>
+    <t xml:space="preserve">Calculé depuis les onglets Dépenses et Ressources. 2027 : charges et refacturations sur T3-T4 (recrutement au 1er juillet), formalités au T1 ; reste à charge (B.3) versé par quarts, comme au planning du fonds ; aide FEAMPA versée sur demande de paiement semestrielle, après service fait et sur factures acquittées. 2030-2031 : seulement la fin de l'opération 2027-2029 (versements FEAMPA restants et remboursement de l'avance), sans les charges de ces exercices.</t>
   </si>
   <si>
     <t xml:space="preserve">HYPOTHÈSES DE TRÉSORERIE</t>
@@ -1303,7 +1303,7 @@
     <t xml:space="preserve">Délai entre la fin du semestre justifié et le versement FEAMPA (trimestres)</t>
   </si>
   <si>
-    <t xml:space="preserve">Environ 1 mois pour constituer la demande de paiement, puis le délai réglementaire de paiement de 80 jours (art. 74 RPDC). Hypothèse retenue, à confirmer avec le service instructeur.</t>
+    <t xml:space="preserve">Délai constaté : un à deux ans entre la demande de paiement et le versement. Hypothèse retenue : deux ans (8 trimestres), à confirmer avec le service instructeur.</t>
   </si>
   <si>
     <t xml:space="preserve">Trésorerie minimale de sécurité</t>
@@ -1372,6 +1372,18 @@
     <t xml:space="preserve">T4 2030</t>
   </si>
   <si>
+    <t xml:space="preserve">T1 2031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2 2031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3 2031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T4 2031</t>
+  </si>
+  <si>
     <t xml:space="preserve">Base de calcul</t>
   </si>
   <si>
@@ -1495,7 +1507,7 @@
     <t xml:space="preserve">Contrôle — avance sous le plafond</t>
   </si>
   <si>
-    <t xml:space="preserve">Intérêts calculés sur la période (2027-2030)</t>
+    <t xml:space="preserve">Intérêts calculés sur la période (2027-2031)</t>
   </si>
   <si>
     <t xml:space="preserve">Intérêts inscrits au budget (Dépenses, ligne 28)</t>
@@ -1804,255 +1816,255 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4928,10 +4940,10 @@
         <v>224</v>
       </c>
       <c r="D129" s="38" t="n">
-        <v>1376</v>
+        <v>2950</v>
       </c>
       <c r="E129" s="38" t="n">
-        <v>1766</v>
+        <v>12942</v>
       </c>
       <c r="F129" s="25" t="s">
         <v>302</v>
@@ -5654,15 +5666,15 @@
       </c>
       <c r="D29" s="49" t="n">
         <f aca="false">Hypothèses!D129</f>
-        <v>1376</v>
+        <v>2950</v>
       </c>
       <c r="E29" s="49" t="n">
         <f aca="false">Hypothèses!E129</f>
-        <v>1766</v>
+        <v>12942</v>
       </c>
       <c r="F29" s="48" t="n">
         <f aca="false">SUM(B29:E29)</f>
-        <v>3366</v>
+        <v>16116</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5679,15 +5691,15 @@
       </c>
       <c r="D30" s="48" t="n">
         <f aca="false">SUM(D23:D29)</f>
-        <v>9338</v>
+        <v>10912</v>
       </c>
       <c r="E30" s="48" t="n">
         <f aca="false">SUM(E23:E29)</f>
-        <v>9825</v>
+        <v>21001</v>
       </c>
       <c r="F30" s="48" t="n">
         <f aca="false">SUM(B30:E30)</f>
-        <v>26705</v>
+        <v>39455</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5704,15 +5716,15 @@
       </c>
       <c r="D32" s="51" t="n">
         <f aca="false">D7+D13+D17+D21+D30</f>
-        <v>106765</v>
+        <v>108339</v>
       </c>
       <c r="E32" s="51" t="n">
         <f aca="false">E7+E13+E17+E21+E30</f>
-        <v>108396.44</v>
+        <v>119572.44</v>
       </c>
       <c r="F32" s="51" t="n">
         <f aca="false">SUM(B32:E32)</f>
-        <v>277668.44</v>
+        <v>290418.44</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6191,15 +6203,15 @@
       </c>
       <c r="D14" s="49" t="n">
         <f aca="false">MAX(0,Dépenses!D32-D8-D10-D11-D12-D13-D15)</f>
-        <v>20546.51832</v>
+        <v>22104.77832</v>
       </c>
       <c r="E14" s="49" t="n">
         <f aca="false">MAX(0,Dépenses!E32-E8-E10-E11-E12-E13-E15)</f>
-        <v>21002.7291744</v>
+        <v>32066.9691744</v>
       </c>
       <c r="F14" s="48" t="n">
         <f aca="false">SUM(B14:E14)</f>
-        <v>56873.9982944</v>
+        <v>69496.4982944</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6216,15 +6228,15 @@
       </c>
       <c r="D15" s="49" t="n">
         <f aca="false">Hypothèses!$B$24*Dépenses!D32</f>
-        <v>1067.65</v>
+        <v>1083.39</v>
       </c>
       <c r="E15" s="49" t="n">
         <f aca="false">Hypothèses!$B$24*Dépenses!E32</f>
-        <v>1083.9644</v>
+        <v>1195.7244</v>
       </c>
       <c r="F15" s="48" t="n">
         <f aca="false">SUM(B15:E15)</f>
-        <v>2776.6844</v>
+        <v>2904.1844</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6241,15 +6253,15 @@
       </c>
       <c r="D16" s="48" t="n">
         <f aca="false">SUM(D10:D15)</f>
-        <v>47859.76832</v>
+        <v>49433.76832</v>
       </c>
       <c r="E16" s="48" t="n">
         <f aca="false">SUM(E10:E15)</f>
-        <v>48824.8695744</v>
+        <v>60000.8695744</v>
       </c>
       <c r="F16" s="48" t="n">
         <f aca="false">SUM(B16:E16)</f>
-        <v>126645.6586944</v>
+        <v>139395.6586944</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6266,15 +6278,15 @@
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">D8+D16</f>
-        <v>106765</v>
+        <v>108339</v>
       </c>
       <c r="E17" s="51" t="n">
         <f aca="false">E8+E16</f>
-        <v>108396.44</v>
+        <v>119572.44</v>
       </c>
       <c r="F17" s="51" t="n">
         <f aca="false">SUM(B17:E17)</f>
-        <v>277668.44</v>
+        <v>290418.44</v>
       </c>
     </row>
   </sheetData>
@@ -6339,15 +6351,15 @@
       </c>
       <c r="D4" s="48" t="n">
         <f aca="false">Dépenses!D32</f>
-        <v>106765</v>
+        <v>108339</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">Dépenses!E32</f>
-        <v>108396.44</v>
+        <v>119572.44</v>
       </c>
       <c r="F4" s="48" t="n">
         <f aca="false">SUM(B4:E4)</f>
-        <v>277668.44</v>
+        <v>290418.44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6364,15 +6376,15 @@
       </c>
       <c r="D5" s="48" t="n">
         <f aca="false">Ressources!D17</f>
-        <v>106765</v>
+        <v>108339</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">Ressources!E17</f>
-        <v>108396.44</v>
+        <v>119572.44</v>
       </c>
       <c r="F5" s="48" t="n">
         <f aca="false">SUM(B5:E5)</f>
-        <v>277668.44</v>
+        <v>290418.44</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6514,15 +6526,15 @@
       </c>
       <c r="D12" s="47" t="n">
         <f aca="false">Dépenses!D30</f>
-        <v>9338</v>
+        <v>10912</v>
       </c>
       <c r="E12" s="47" t="n">
         <f aca="false">Dépenses!E30</f>
-        <v>9825</v>
+        <v>21001</v>
       </c>
       <c r="F12" s="48" t="n">
         <f aca="false">SUM(B12:E12)</f>
-        <v>26705</v>
+        <v>39455</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6614,15 +6626,15 @@
       </c>
       <c r="D17" s="47" t="n">
         <f aca="false">Ressources!D14</f>
-        <v>20546.51832</v>
+        <v>22104.77832</v>
       </c>
       <c r="E17" s="47" t="n">
         <f aca="false">Ressources!E14</f>
-        <v>21002.7291744</v>
+        <v>32066.9691744</v>
       </c>
       <c r="F17" s="48" t="n">
         <f aca="false">SUM(B17:E17)</f>
-        <v>56873.9982944</v>
+        <v>69496.4982944</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6639,15 +6651,15 @@
       </c>
       <c r="D18" s="47" t="n">
         <f aca="false">Ressources!D15</f>
-        <v>1067.65</v>
+        <v>1083.39</v>
       </c>
       <c r="E18" s="47" t="n">
         <f aca="false">Ressources!E15</f>
-        <v>1083.9644</v>
+        <v>1195.7244</v>
       </c>
       <c r="F18" s="48" t="n">
         <f aca="false">SUM(B18:E18)</f>
-        <v>2776.6844</v>
+        <v>2904.1844</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6665,15 +6677,15 @@
       </c>
       <c r="D20" s="53" t="n">
         <f aca="false">IFERROR(D14/D4,0)</f>
-        <v>0.551727922821149</v>
+        <v>0.543712159794718</v>
       </c>
       <c r="E20" s="53" t="n">
         <f aca="false">IFERROR(E14/E4,0)</f>
-        <v>0.549571281359425</v>
+        <v>0.498204857453774</v>
       </c>
       <c r="F20" s="54" t="n">
         <f aca="false">IFERROR(F14/F4,0)</f>
-        <v>0.543896098907027</v>
+        <v>0.520017879393609</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6690,15 +6702,15 @@
       </c>
       <c r="D21" s="53" t="n">
         <f aca="false">IFERROR(D8/D4,0)</f>
-        <v>0.550573689879642</v>
+        <v>0.54257469609282</v>
       </c>
       <c r="E21" s="53" t="n">
         <f aca="false">IFERROR(E8/E4,0)</f>
-        <v>0.552845093436648</v>
+        <v>0.501172678252614</v>
       </c>
       <c r="F21" s="54" t="n">
         <f aca="false">IFERROR(F8/F4,0)</f>
-        <v>0.531347530889719</v>
+        <v>0.508020220754577</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6707,7 +6719,7 @@
       </c>
       <c r="F22" s="48" t="n">
         <f aca="false">IFERROR(F4/3,0)</f>
-        <v>92556.1466666667</v>
+        <v>96806.1466666667</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6724,15 +6736,15 @@
       </c>
       <c r="D23" s="53" t="n">
         <f aca="false">IFERROR((D15+D17)/D4,0)</f>
-        <v>0.315359137545076</v>
+        <v>0.325160637628186</v>
       </c>
       <c r="E23" s="53" t="n">
         <f aca="false">IFERROR((E15+E17)/E4,0)</f>
-        <v>0.317093598040674</v>
+        <v>0.379987705983084</v>
       </c>
       <c r="F23" s="54" t="n">
         <f aca="false">IFERROR((F15+F17)/F4,0)</f>
-        <v>0.325465459071978</v>
+        <v>0.354639968090181</v>
       </c>
     </row>
   </sheetData>
@@ -7560,12 +7572,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="2" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="19" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7592,7 +7605,7 @@
         <v>424</v>
       </c>
       <c r="B5" s="59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>425</v>
@@ -7685,20 +7698,32 @@
         <v>447</v>
       </c>
       <c r="R10" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="S10" s="46" t="s">
+        <v>449</v>
+      </c>
+      <c r="T10" s="46" t="s">
+        <v>450</v>
+      </c>
+      <c r="U10" s="46" t="s">
+        <v>451</v>
+      </c>
+      <c r="V10" s="46" t="s">
         <v>313</v>
       </c>
-      <c r="S10" s="46" t="s">
-        <v>448</v>
+      <c r="W10" s="46" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B12" s="47" t="n">
         <v>0</v>
@@ -7758,17 +7783,29 @@
       <c r="Q12" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R12" s="48" t="n">
-        <f aca="false">SUM(B12:Q12)</f>
+      <c r="R12" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="48" t="n">
+        <f aca="false">SUM(B12:U12)</f>
         <v>33497.488</v>
       </c>
-      <c r="S12" s="62" t="s">
-        <v>451</v>
+      <c r="W12" s="62" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B13" s="47" t="n">
         <v>0</v>
@@ -7828,17 +7865,29 @@
       <c r="Q13" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="48" t="n">
-        <f aca="false">SUM(B13:Q13)</f>
+      <c r="R13" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="48" t="n">
+        <f aca="false">SUM(B13:U13)</f>
         <v>33497.488</v>
       </c>
-      <c r="S13" s="62" t="s">
-        <v>453</v>
+      <c r="W13" s="62" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B14" s="47" t="n">
         <f aca="false">(Ressources!C14)/4</f>
@@ -7858,35 +7907,35 @@
       </c>
       <c r="F14" s="47" t="n">
         <f aca="false">(Ressources!D14)/4</f>
-        <v>5136.62958</v>
+        <v>5526.19458</v>
       </c>
       <c r="G14" s="47" t="n">
         <f aca="false">(Ressources!D14)/4</f>
-        <v>5136.62958</v>
+        <v>5526.19458</v>
       </c>
       <c r="H14" s="47" t="n">
         <f aca="false">(Ressources!D14)/4</f>
-        <v>5136.62958</v>
+        <v>5526.19458</v>
       </c>
       <c r="I14" s="47" t="n">
         <f aca="false">(Ressources!D14)/4</f>
-        <v>5136.62958</v>
+        <v>5526.19458</v>
       </c>
       <c r="J14" s="47" t="n">
         <f aca="false">(Ressources!E14)/4</f>
-        <v>5250.6822936</v>
+        <v>8016.7422936</v>
       </c>
       <c r="K14" s="47" t="n">
         <f aca="false">(Ressources!E14)/4</f>
-        <v>5250.6822936</v>
+        <v>8016.7422936</v>
       </c>
       <c r="L14" s="47" t="n">
         <f aca="false">(Ressources!E14)/4</f>
-        <v>5250.6822936</v>
+        <v>8016.7422936</v>
       </c>
       <c r="M14" s="47" t="n">
         <f aca="false">(Ressources!E14)/4</f>
-        <v>5250.6822936</v>
+        <v>8016.7422936</v>
       </c>
       <c r="N14" s="47" t="n">
         <v>0</v>
@@ -7900,17 +7949,29 @@
       <c r="Q14" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R14" s="48" t="n">
-        <f aca="false">SUM(B14:Q14)</f>
-        <v>56873.9982944</v>
-      </c>
-      <c r="S14" s="62" t="s">
-        <v>455</v>
+      <c r="R14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="48" t="n">
+        <f aca="false">SUM(B14:U14)</f>
+        <v>69496.4982944</v>
+      </c>
+      <c r="W14" s="62" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B15" s="47" t="n">
         <f aca="false">Ressources!C15</f>
@@ -7927,7 +7988,7 @@
       </c>
       <c r="F15" s="47" t="n">
         <f aca="false">Ressources!D15</f>
-        <v>1067.65</v>
+        <v>1083.39</v>
       </c>
       <c r="G15" s="47" t="n">
         <v>0</v>
@@ -7940,7 +8001,7 @@
       </c>
       <c r="J15" s="47" t="n">
         <f aca="false">Ressources!E15</f>
-        <v>1083.9644</v>
+        <v>1195.7244</v>
       </c>
       <c r="K15" s="47" t="n">
         <v>0</v>
@@ -7963,17 +8024,29 @@
       <c r="Q15" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R15" s="48" t="n">
-        <f aca="false">SUM(B15:Q15)</f>
-        <v>2776.6844</v>
-      </c>
-      <c r="S15" s="62" t="s">
-        <v>457</v>
+      <c r="R15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="48" t="n">
+        <f aca="false">SUM(B15:U15)</f>
+        <v>2904.1844</v>
+      </c>
+      <c r="W15" s="62" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(B36,0,-$B$5),0)</f>
@@ -7993,7 +8066,7 @@
       </c>
       <c r="F16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(F36,0,-$B$5),0)</f>
-        <v>32545.9792</v>
+        <v>0</v>
       </c>
       <c r="G16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(G36,0,-$B$5),0)</f>
@@ -8001,7 +8074,7 @@
       </c>
       <c r="H16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(H36,0,-$B$5),0)</f>
-        <v>29452.61584</v>
+        <v>0</v>
       </c>
       <c r="I16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(I36,0,-$B$5),0)</f>
@@ -8009,7 +8082,7 @@
       </c>
       <c r="J16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(J36,0,-$B$5),0)</f>
-        <v>29452.61584</v>
+        <v>0</v>
       </c>
       <c r="K16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(K36,0,-$B$5),0)</f>
@@ -8017,19 +8090,19 @@
       </c>
       <c r="L16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(L36,0,-$B$5),0)</f>
-        <v>29785.7852128</v>
+        <v>0</v>
       </c>
       <c r="M16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(M36,0,-$B$5),0)</f>
-        <v>0</v>
+        <v>32545.9792</v>
       </c>
       <c r="N16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(N36,0,-$B$5),0)</f>
-        <v>29785.7852128</v>
+        <v>0</v>
       </c>
       <c r="O16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(O36,0,-$B$5),0)</f>
-        <v>0</v>
+        <v>29452.61584</v>
       </c>
       <c r="P16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(P36,0,-$B$5),0)</f>
@@ -8037,19 +8110,35 @@
       </c>
       <c r="Q16" s="47" t="n">
         <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(Q36,0,-$B$5),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="48" t="n">
-        <f aca="false">SUM(B16:Q16)</f>
+        <v>29452.61584</v>
+      </c>
+      <c r="R16" s="47" t="n">
+        <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(R36,0,-$B$5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="47" t="n">
+        <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(S36,0,-$B$5),0)</f>
+        <v>29785.7852128</v>
+      </c>
+      <c r="T16" s="47" t="n">
+        <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(T36,0,-$B$5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U16" s="47" t="n">
+        <f aca="true">IF(COLUMN()-COLUMN($B$36)&gt;=$B$5,OFFSET(U36,0,-$B$5),0)</f>
+        <v>29785.7852128</v>
+      </c>
+      <c r="V16" s="48" t="n">
+        <f aca="false">SUM(B16:U16)</f>
         <v>151022.7813056</v>
       </c>
-      <c r="S16" s="62" t="s">
-        <v>459</v>
+      <c r="W16" s="62" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B17" s="48" t="n">
         <f aca="false">SUM(B12:B16)</f>
@@ -8069,43 +8158,43 @@
       </c>
       <c r="F17" s="48" t="n">
         <f aca="false">SUM(F12:F16)</f>
-        <v>45311.65878</v>
+        <v>13170.98458</v>
       </c>
       <c r="G17" s="48" t="n">
         <f aca="false">SUM(G12:G16)</f>
-        <v>11698.02958</v>
+        <v>12087.59458</v>
       </c>
       <c r="H17" s="48" t="n">
         <f aca="false">SUM(H12:H16)</f>
-        <v>41150.64542</v>
+        <v>12087.59458</v>
       </c>
       <c r="I17" s="48" t="n">
         <f aca="false">SUM(I12:I16)</f>
-        <v>11698.02958</v>
+        <v>12087.59458</v>
       </c>
       <c r="J17" s="48" t="n">
         <f aca="false">SUM(J12:J16)</f>
-        <v>42471.8065336</v>
+        <v>15897.0106936</v>
       </c>
       <c r="K17" s="48" t="n">
         <f aca="false">SUM(K12:K16)</f>
-        <v>11935.2262936</v>
+        <v>14701.2862936</v>
       </c>
       <c r="L17" s="48" t="n">
         <f aca="false">SUM(L12:L16)</f>
-        <v>41721.0115064</v>
+        <v>14701.2862936</v>
       </c>
       <c r="M17" s="48" t="n">
         <f aca="false">SUM(M12:M16)</f>
-        <v>11935.2262936</v>
+        <v>47247.2654936</v>
       </c>
       <c r="N17" s="48" t="n">
         <f aca="false">SUM(N12:N16)</f>
-        <v>29785.7852128</v>
+        <v>0</v>
       </c>
       <c r="O17" s="48" t="n">
         <f aca="false">SUM(O12:O16)</f>
-        <v>0</v>
+        <v>29452.61584</v>
       </c>
       <c r="P17" s="48" t="n">
         <f aca="false">SUM(P12:P16)</f>
@@ -8113,21 +8202,37 @@
       </c>
       <c r="Q17" s="48" t="n">
         <f aca="false">SUM(Q12:Q16)</f>
-        <v>0</v>
+        <v>29452.61584</v>
       </c>
       <c r="R17" s="48" t="n">
-        <f aca="false">SUM(B17:Q17)</f>
-        <v>277668.44</v>
+        <f aca="false">SUM(R12:R16)</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="48" t="n">
+        <f aca="false">SUM(S12:S16)</f>
+        <v>29785.7852128</v>
+      </c>
+      <c r="T17" s="48" t="n">
+        <f aca="false">SUM(T12:T16)</f>
+        <v>0</v>
+      </c>
+      <c r="U17" s="48" t="n">
+        <f aca="false">SUM(U12:U16)</f>
+        <v>29785.7852128</v>
+      </c>
+      <c r="V17" s="48" t="n">
+        <f aca="false">SUM(B17:U17)</f>
+        <v>290418.44</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B19" s="47" t="n">
         <v>0</v>
@@ -8187,17 +8292,29 @@
       <c r="Q19" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R19" s="48" t="n">
-        <f aca="false">SUM(B19:Q19)</f>
+      <c r="R19" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="48" t="n">
+        <f aca="false">SUM(B19:U19)</f>
         <v>147538.44</v>
       </c>
-      <c r="S19" s="62" t="s">
-        <v>463</v>
+      <c r="W19" s="62" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B20" s="47" t="n">
         <f aca="false">N(Hypothèses!C43)</f>
@@ -8258,17 +8375,29 @@
       <c r="Q20" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R20" s="48" t="n">
-        <f aca="false">SUM(B20:Q20)</f>
+      <c r="R20" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="48" t="n">
+        <f aca="false">SUM(B20:U20)</f>
         <v>71175</v>
       </c>
-      <c r="S20" s="62" t="s">
-        <v>465</v>
+      <c r="W20" s="62" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B21" s="47" t="n">
         <v>0</v>
@@ -8328,14 +8457,26 @@
       <c r="Q21" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R21" s="48" t="n">
-        <f aca="false">SUM(B21:Q21)</f>
+      <c r="R21" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="48" t="n">
+        <f aca="false">SUM(B21:U21)</f>
         <v>28950</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B22" s="47" t="n">
         <v>0</v>
@@ -8395,14 +8536,26 @@
       <c r="Q22" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R22" s="48" t="n">
-        <f aca="false">SUM(B22:Q22)</f>
+      <c r="R22" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="48" t="n">
+        <f aca="false">SUM(B22:U22)</f>
         <v>3300</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B23" s="47" t="n">
         <v>0</v>
@@ -8462,14 +8615,26 @@
       <c r="Q23" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="48" t="n">
-        <f aca="false">SUM(B23:Q23)</f>
+      <c r="R23" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="48" t="n">
+        <f aca="false">SUM(B23:U23)</f>
         <v>23339</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B24" s="47" t="n">
         <f aca="false">0</f>
@@ -8493,59 +8658,75 @@
       </c>
       <c r="G24" s="47" t="n">
         <f aca="false">F32*$B$7/4</f>
-        <v>238.135506217341</v>
+        <v>639.893933717341</v>
       </c>
       <c r="H24" s="47" t="n">
         <f aca="false">G32*$B$7/4</f>
-        <v>424.227455295058</v>
+        <v>826.138300638808</v>
       </c>
       <c r="I24" s="47" t="n">
         <f aca="false">H32*$B$7/4</f>
-        <v>244.487855736246</v>
+        <v>1014.71072214679</v>
       </c>
       <c r="J24" s="47" t="n">
         <f aca="false">I32*$B$7/4</f>
-        <v>430.659209182949</v>
+        <v>1205.64029892363</v>
       </c>
       <c r="K24" s="47" t="n">
         <f aca="false">J32*$B$7/4</f>
-        <v>238.364992627736</v>
+        <v>1355.21829399017</v>
       </c>
       <c r="L24" s="47" t="n">
         <f aca="false">K32*$B$7/4</f>
-        <v>425.374351365583</v>
+        <v>1521.61256899505</v>
       </c>
       <c r="M24" s="47" t="n">
         <f aca="false">L32*$B$7/4</f>
-        <v>242.399011927653</v>
+        <v>1690.08677243749</v>
       </c>
       <c r="N24" s="47" t="n">
         <f aca="false">M32*$B$7/4</f>
-        <v>429.458795906749</v>
+        <v>1453.84216342296</v>
       </c>
       <c r="O24" s="47" t="n">
         <f aca="false">N32*$B$7/4</f>
-        <v>0.0047156955828541</v>
+        <v>1409.51519046574</v>
       </c>
       <c r="P24" s="47" t="n">
         <f aca="false">O32*$B$7/4</f>
-        <v>0.00477464177763977</v>
+        <v>1058.97643234657</v>
       </c>
       <c r="Q24" s="47" t="n">
         <f aca="false">P32*$B$7/4</f>
-        <v>0.00483432479986027</v>
-      </c>
-      <c r="R24" s="48" t="n">
-        <f aca="false">SUM(B24:Q24)</f>
-        <v>3366.39158030878</v>
-      </c>
-      <c r="S24" s="62" t="s">
-        <v>470</v>
+        <v>1072.2136377509</v>
+      </c>
+      <c r="R24" s="47" t="n">
+        <f aca="false">Q32*$B$7/4</f>
+        <v>717.458610222784</v>
+      </c>
+      <c r="S24" s="47" t="n">
+        <f aca="false">R32*$B$7/4</f>
+        <v>726.426842850569</v>
+      </c>
+      <c r="T24" s="47" t="n">
+        <f aca="false">S32*$B$7/4</f>
+        <v>363.184863226201</v>
+      </c>
+      <c r="U24" s="47" t="n">
+        <f aca="false">T32*$B$7/4</f>
+        <v>367.724674016529</v>
+      </c>
+      <c r="V24" s="48" t="n">
+        <f aca="false">SUM(B24:U24)</f>
+        <v>16115.9133825388</v>
+      </c>
+      <c r="W24" s="62" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B25" s="48" t="n">
         <f aca="false">SUM(B19:B24)</f>
@@ -8569,57 +8750,73 @@
       </c>
       <c r="G25" s="48" t="n">
         <f aca="false">SUM(G19:G24)</f>
-        <v>26585.3855062173</v>
+        <v>26987.1439337173</v>
       </c>
       <c r="H25" s="48" t="n">
         <f aca="false">SUM(H19:H24)</f>
-        <v>26771.4774552951</v>
+        <v>27173.3883006388</v>
       </c>
       <c r="I25" s="48" t="n">
         <f aca="false">SUM(I19:I24)</f>
-        <v>26591.7378557362</v>
+        <v>27361.9607221468</v>
       </c>
       <c r="J25" s="48" t="n">
         <f aca="false">SUM(J19:J24)</f>
-        <v>27088.269209183</v>
+        <v>27863.2502989236</v>
       </c>
       <c r="K25" s="48" t="n">
         <f aca="false">SUM(K19:K24)</f>
-        <v>26895.9749926277</v>
+        <v>28012.8282939902</v>
       </c>
       <c r="L25" s="48" t="n">
         <f aca="false">SUM(L19:L24)</f>
-        <v>27082.9843513656</v>
+        <v>28179.2225689951</v>
       </c>
       <c r="M25" s="48" t="n">
         <f aca="false">SUM(M19:M24)</f>
-        <v>26900.0090119277</v>
+        <v>28347.6967724375</v>
       </c>
       <c r="N25" s="48" t="n">
         <f aca="false">SUM(N19:N24)</f>
-        <v>429.458795906749</v>
+        <v>1453.84216342296</v>
       </c>
       <c r="O25" s="48" t="n">
         <f aca="false">SUM(O19:O24)</f>
-        <v>0.0047156955828541</v>
+        <v>1409.51519046574</v>
       </c>
       <c r="P25" s="48" t="n">
         <f aca="false">SUM(P19:P24)</f>
-        <v>0.00477464177763977</v>
+        <v>1058.97643234657</v>
       </c>
       <c r="Q25" s="48" t="n">
         <f aca="false">SUM(Q19:Q24)</f>
-        <v>0.00483432479986027</v>
+        <v>1072.2136377509</v>
       </c>
       <c r="R25" s="48" t="n">
-        <f aca="false">SUM(B25:Q25)</f>
-        <v>277668.831580309</v>
+        <f aca="false">SUM(R19:R24)</f>
+        <v>717.458610222784</v>
+      </c>
+      <c r="S25" s="48" t="n">
+        <f aca="false">SUM(S19:S24)</f>
+        <v>726.426842850569</v>
+      </c>
+      <c r="T25" s="48" t="n">
+        <f aca="false">SUM(T19:T24)</f>
+        <v>363.184863226201</v>
+      </c>
+      <c r="U25" s="48" t="n">
+        <f aca="false">SUM(U19:U24)</f>
+        <v>367.724674016529</v>
+      </c>
+      <c r="V25" s="48" t="n">
+        <f aca="false">SUM(B25:U25)</f>
+        <v>290418.353382539</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B27" s="48" t="n">
         <f aca="false">B17-B25</f>
@@ -8639,60 +8836,76 @@
       </c>
       <c r="F27" s="48" t="n">
         <f aca="false">F17-F25</f>
-        <v>18495.0847148471</v>
+        <v>-13645.5894851529</v>
       </c>
       <c r="G27" s="48" t="n">
         <f aca="false">G17-G25</f>
-        <v>-14887.3559262173</v>
+        <v>-14899.5493537173</v>
       </c>
       <c r="H27" s="48" t="n">
         <f aca="false">H17-H25</f>
-        <v>14379.1679647049</v>
+        <v>-15085.7937206388</v>
       </c>
       <c r="I27" s="48" t="n">
         <f aca="false">I17-I25</f>
-        <v>-14893.7082757362</v>
+        <v>-15274.3661421468</v>
       </c>
       <c r="J27" s="48" t="n">
         <f aca="false">J17-J25</f>
-        <v>15383.5373244171</v>
+        <v>-11966.2396053236</v>
       </c>
       <c r="K27" s="48" t="n">
         <f aca="false">K17-K25</f>
-        <v>-14960.7486990277</v>
+        <v>-13311.5420003902</v>
       </c>
       <c r="L27" s="48" t="n">
         <f aca="false">L17-L25</f>
-        <v>14638.0271550344</v>
+        <v>-13477.9362753951</v>
       </c>
       <c r="M27" s="48" t="n">
         <f aca="false">M17-M25</f>
-        <v>-14964.7827183277</v>
+        <v>18899.5687211625</v>
       </c>
       <c r="N27" s="48" t="n">
         <f aca="false">N17-N25</f>
-        <v>29356.3264168933</v>
+        <v>-1453.84216342296</v>
       </c>
       <c r="O27" s="48" t="n">
         <f aca="false">O17-O25</f>
-        <v>-0.0047156955828541</v>
+        <v>28043.1006495343</v>
       </c>
       <c r="P27" s="48" t="n">
         <f aca="false">P17-P25</f>
-        <v>-0.00477464177763977</v>
+        <v>-1058.97643234657</v>
       </c>
       <c r="Q27" s="48" t="n">
         <f aca="false">Q17-Q25</f>
-        <v>-0.00483432479986027</v>
+        <v>28380.4022022491</v>
       </c>
       <c r="R27" s="48" t="n">
-        <f aca="false">SUM(B27:Q27)</f>
-        <v>-0.391580308787318</v>
+        <f aca="false">R17-R25</f>
+        <v>-717.458610222784</v>
+      </c>
+      <c r="S27" s="48" t="n">
+        <f aca="false">S17-S25</f>
+        <v>29059.3583699494</v>
+      </c>
+      <c r="T27" s="48" t="n">
+        <f aca="false">T17-T25</f>
+        <v>-363.184863226201</v>
+      </c>
+      <c r="U27" s="48" t="n">
+        <f aca="false">U17-U25</f>
+        <v>29418.0605387835</v>
+      </c>
+      <c r="V27" s="48" t="n">
+        <f aca="false">SUM(B27:U27)</f>
+        <v>0.0866174611801398</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B28" s="47" t="n">
         <f aca="false">B27</f>
@@ -8712,62 +8925,78 @@
       </c>
       <c r="F28" s="47" t="n">
         <f aca="false">E33+F27</f>
-        <v>23495.0847148471</v>
+        <v>-8645.58948515293</v>
       </c>
       <c r="G28" s="47" t="n">
         <f aca="false">F33+G27</f>
-        <v>-9887.35592621734</v>
+        <v>-9899.54935371734</v>
       </c>
       <c r="H28" s="47" t="n">
         <f aca="false">G33+H27</f>
-        <v>19379.1679647049</v>
+        <v>-10085.7937206388</v>
       </c>
       <c r="I28" s="47" t="n">
         <f aca="false">H33+I27</f>
-        <v>-9893.70827573625</v>
+        <v>-10274.3661421468</v>
       </c>
       <c r="J28" s="47" t="n">
         <f aca="false">I33+J27</f>
-        <v>20383.5373244171</v>
+        <v>-6966.23960532363</v>
       </c>
       <c r="K28" s="47" t="n">
         <f aca="false">J33+K27</f>
-        <v>-9960.74869902774</v>
+        <v>-8311.54200039017</v>
       </c>
       <c r="L28" s="47" t="n">
         <f aca="false">K33+L27</f>
-        <v>19638.0271550344</v>
+        <v>-8477.93627539505</v>
       </c>
       <c r="M28" s="47" t="n">
         <f aca="false">L33+M27</f>
-        <v>-9964.78271832765</v>
+        <v>23899.5687211625</v>
       </c>
       <c r="N28" s="47" t="n">
         <f aca="false">M33+N27</f>
-        <v>34356.3264168933</v>
+        <v>3546.15783657704</v>
       </c>
       <c r="O28" s="47" t="n">
         <f aca="false">N33+O27</f>
-        <v>-0.0047156955828541</v>
+        <v>28043.1006495343</v>
       </c>
       <c r="P28" s="47" t="n">
         <f aca="false">O33+P27</f>
-        <v>-0.00477464177763977</v>
+        <v>-1058.97643234657</v>
       </c>
       <c r="Q28" s="47" t="n">
         <f aca="false">P33+Q27</f>
-        <v>-0.00483432479986027</v>
-      </c>
-      <c r="R28" s="48"/>
+        <v>28380.4022022491</v>
+      </c>
+      <c r="R28" s="47" t="n">
+        <f aca="false">Q33+R27</f>
+        <v>-717.458610222784</v>
+      </c>
+      <c r="S28" s="47" t="n">
+        <f aca="false">R33+S27</f>
+        <v>29059.3583699494</v>
+      </c>
+      <c r="T28" s="47" t="n">
+        <f aca="false">S33+T27</f>
+        <v>-363.184863226201</v>
+      </c>
+      <c r="U28" s="47" t="n">
+        <f aca="false">T33+U27</f>
+        <v>29418.0605387835</v>
+      </c>
+      <c r="V28" s="48"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="36" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B30" s="47" t="n">
         <f aca="false">MAX(0,$B$6-B28)</f>
@@ -8787,35 +9016,35 @@
       </c>
       <c r="F30" s="47" t="n">
         <f aca="false">MAX(0,$B$6-F28)</f>
-        <v>0</v>
+        <v>13645.5894851529</v>
       </c>
       <c r="G30" s="47" t="n">
         <f aca="false">MAX(0,$B$6-G28)</f>
-        <v>14887.3559262173</v>
+        <v>14899.5493537173</v>
       </c>
       <c r="H30" s="47" t="n">
         <f aca="false">MAX(0,$B$6-H28)</f>
-        <v>0</v>
+        <v>15085.7937206388</v>
       </c>
       <c r="I30" s="47" t="n">
         <f aca="false">MAX(0,$B$6-I28)</f>
-        <v>14893.7082757362</v>
+        <v>15274.3661421468</v>
       </c>
       <c r="J30" s="47" t="n">
         <f aca="false">MAX(0,$B$6-J28)</f>
-        <v>0</v>
+        <v>11966.2396053236</v>
       </c>
       <c r="K30" s="47" t="n">
         <f aca="false">MAX(0,$B$6-K28)</f>
-        <v>14960.7486990277</v>
+        <v>13311.5420003902</v>
       </c>
       <c r="L30" s="47" t="n">
         <f aca="false">MAX(0,$B$6-L28)</f>
-        <v>0</v>
+        <v>13477.9362753951</v>
       </c>
       <c r="M30" s="47" t="n">
         <f aca="false">MAX(0,$B$6-M28)</f>
-        <v>14964.7827183277</v>
+        <v>0</v>
       </c>
       <c r="N30" s="47" t="n">
         <f aca="false">MAX(0,0-N28)</f>
@@ -8823,27 +9052,43 @@
       </c>
       <c r="O30" s="47" t="n">
         <f aca="false">MAX(0,0-O28)</f>
-        <v>0.0047156955828541</v>
+        <v>0</v>
       </c>
       <c r="P30" s="47" t="n">
         <f aca="false">MAX(0,0-P28)</f>
-        <v>0.00477464177763977</v>
+        <v>1058.97643234657</v>
       </c>
       <c r="Q30" s="47" t="n">
         <f aca="false">MAX(0,0-Q28)</f>
-        <v>0.00483432479986027</v>
-      </c>
-      <c r="R30" s="48" t="n">
-        <f aca="false">SUM(B30:Q30)</f>
-        <v>98026.2774562055</v>
-      </c>
-      <c r="S30" s="62" t="s">
-        <v>476</v>
+        <v>0</v>
+      </c>
+      <c r="R30" s="47" t="n">
+        <f aca="false">MAX(0,0-R28)</f>
+        <v>717.458610222784</v>
+      </c>
+      <c r="S30" s="47" t="n">
+        <f aca="false">MAX(0,0-S28)</f>
+        <v>0</v>
+      </c>
+      <c r="T30" s="47" t="n">
+        <f aca="false">MAX(0,0-T28)</f>
+        <v>363.184863226201</v>
+      </c>
+      <c r="U30" s="47" t="n">
+        <f aca="false">MAX(0,0-U28)</f>
+        <v>0</v>
+      </c>
+      <c r="V30" s="48" t="n">
+        <f aca="false">SUM(B30:U30)</f>
+        <v>138120.304000795</v>
+      </c>
+      <c r="W30" s="62" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B31" s="47" t="n">
         <f aca="false">0</f>
@@ -8863,7 +9108,7 @@
       </c>
       <c r="F31" s="47" t="n">
         <f aca="false">MIN(E32,MAX(0,F28-$B$6))</f>
-        <v>18495.0847148471</v>
+        <v>0</v>
       </c>
       <c r="G31" s="47" t="n">
         <f aca="false">MIN(F32,MAX(0,G28-$B$6))</f>
@@ -8871,7 +9116,7 @@
       </c>
       <c r="H31" s="47" t="n">
         <f aca="false">MIN(G32,MAX(0,H28-$B$6))</f>
-        <v>14379.1679647049</v>
+        <v>0</v>
       </c>
       <c r="I31" s="47" t="n">
         <f aca="false">MIN(H32,MAX(0,I28-$B$6))</f>
@@ -8879,7 +9124,7 @@
       </c>
       <c r="J31" s="47" t="n">
         <f aca="false">MIN(I32,MAX(0,J28-$B$6))</f>
-        <v>15383.5373244171</v>
+        <v>0</v>
       </c>
       <c r="K31" s="47" t="n">
         <f aca="false">MIN(J32,MAX(0,K28-$B$6))</f>
@@ -8887,19 +9132,19 @@
       </c>
       <c r="L31" s="47" t="n">
         <f aca="false">MIN(K32,MAX(0,L28-$B$6))</f>
-        <v>14638.0271550344</v>
+        <v>0</v>
       </c>
       <c r="M31" s="47" t="n">
         <f aca="false">MIN(L32,MAX(0,M28-$B$6))</f>
-        <v>0</v>
+        <v>18899.5687211625</v>
       </c>
       <c r="N31" s="47" t="n">
         <f aca="false">MIN(M32,MAX(0,N28-0))</f>
-        <v>34356.3264168933</v>
+        <v>3546.15783657704</v>
       </c>
       <c r="O31" s="47" t="n">
         <f aca="false">MIN(N32,MAX(0,O28-0))</f>
-        <v>0</v>
+        <v>28043.1006495343</v>
       </c>
       <c r="P31" s="47" t="n">
         <f aca="false">MIN(O32,MAX(0,P28-0))</f>
@@ -8907,19 +9152,35 @@
       </c>
       <c r="Q31" s="47" t="n">
         <f aca="false">MIN(P32,MAX(0,Q28-0))</f>
-        <v>0</v>
-      </c>
-      <c r="R31" s="48" t="n">
-        <f aca="false">SUM(B31:Q31)</f>
-        <v>98025.8858758967</v>
-      </c>
-      <c r="S31" s="62" t="s">
-        <v>478</v>
+        <v>28380.4022022491</v>
+      </c>
+      <c r="R31" s="47" t="n">
+        <f aca="false">MIN(Q32,MAX(0,R28-0))</f>
+        <v>0</v>
+      </c>
+      <c r="S31" s="47" t="n">
+        <f aca="false">MIN(R32,MAX(0,S28-0))</f>
+        <v>29059.3583699494</v>
+      </c>
+      <c r="T31" s="47" t="n">
+        <f aca="false">MIN(S32,MAX(0,T28-0))</f>
+        <v>0</v>
+      </c>
+      <c r="U31" s="47" t="n">
+        <f aca="false">MIN(T32,MAX(0,U28-0))</f>
+        <v>29417.9739213223</v>
+      </c>
+      <c r="V31" s="48" t="n">
+        <f aca="false">SUM(B31:U31)</f>
+        <v>138120.304000795</v>
+      </c>
+      <c r="W31" s="62" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B32" s="48" t="n">
         <f aca="false">B30-B31</f>
@@ -8939,57 +9200,73 @@
       </c>
       <c r="F32" s="48" t="n">
         <f aca="false">E32+F30-F31</f>
-        <v>19050.8404973873</v>
+        <v>51191.5146973873</v>
       </c>
       <c r="G32" s="48" t="n">
         <f aca="false">F32+G30-G31</f>
-        <v>33938.1964236047</v>
+        <v>66091.0640511047</v>
       </c>
       <c r="H32" s="48" t="n">
         <f aca="false">G32+H30-H31</f>
-        <v>19559.0284588997</v>
+        <v>81176.8577717435</v>
       </c>
       <c r="I32" s="48" t="n">
         <f aca="false">H32+I30-I31</f>
-        <v>34452.736734636</v>
+        <v>96451.2239138903</v>
       </c>
       <c r="J32" s="48" t="n">
         <f aca="false">I32+J30-J31</f>
-        <v>19069.1994102189</v>
+        <v>108417.463519214</v>
       </c>
       <c r="K32" s="48" t="n">
         <f aca="false">J32+K30-K31</f>
-        <v>34029.9481092466</v>
+        <v>121729.005519604</v>
       </c>
       <c r="L32" s="48" t="n">
         <f aca="false">K32+L30-L31</f>
-        <v>19391.9209542122</v>
+        <v>135206.941794999</v>
       </c>
       <c r="M32" s="48" t="n">
         <f aca="false">L32+M30-M31</f>
-        <v>34356.7036725399</v>
+        <v>116307.373073837</v>
       </c>
       <c r="N32" s="48" t="n">
         <f aca="false">M32+N30-N31</f>
-        <v>0.377255646628328</v>
+        <v>112761.21523726</v>
       </c>
       <c r="O32" s="48" t="n">
         <f aca="false">N32+O30-O31</f>
-        <v>0.381971342211182</v>
+        <v>84718.1145877253</v>
       </c>
       <c r="P32" s="48" t="n">
         <f aca="false">O32+P30-P31</f>
-        <v>0.386745983988822</v>
+        <v>85777.0910200718</v>
       </c>
       <c r="Q32" s="48" t="n">
         <f aca="false">P32+Q30-Q31</f>
-        <v>0.391580308788682</v>
-      </c>
-      <c r="R32" s="48"/>
+        <v>57396.6888178227</v>
+      </c>
+      <c r="R32" s="48" t="n">
+        <f aca="false">Q32+R30-R31</f>
+        <v>58114.1474280455</v>
+      </c>
+      <c r="S32" s="48" t="n">
+        <f aca="false">R32+S30-S31</f>
+        <v>29054.7890580961</v>
+      </c>
+      <c r="T32" s="48" t="n">
+        <f aca="false">S32+T30-T31</f>
+        <v>29417.9739213223</v>
+      </c>
+      <c r="U32" s="48" t="n">
+        <f aca="false">T32+U30-U31</f>
+        <v>0</v>
+      </c>
+      <c r="V32" s="48"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="33" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B33" s="48" t="n">
         <f aca="false">B28+B30-B31</f>
@@ -9055,17 +9332,33 @@
         <f aca="false">Q28+Q30-Q31</f>
         <v>0</v>
       </c>
-      <c r="R33" s="48"/>
+      <c r="R33" s="48" t="n">
+        <f aca="false">R28+R30-R31</f>
+        <v>0</v>
+      </c>
+      <c r="S33" s="48" t="n">
+        <f aca="false">S28+S30-S31</f>
+        <v>0</v>
+      </c>
+      <c r="T33" s="48" t="n">
+        <f aca="false">T28+T30-T31</f>
+        <v>0</v>
+      </c>
+      <c r="U33" s="48" t="n">
+        <f aca="false">U28+U30-U31</f>
+        <v>0.0866174611837778</v>
+      </c>
+      <c r="V33" s="48"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="36" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B36" s="47" t="n">
         <v>0</v>
@@ -9120,17 +9413,29 @@
       <c r="Q36" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="R36" s="48" t="n">
-        <f aca="false">SUM(B36:Q36)</f>
+      <c r="R36" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="48" t="n">
+        <f aca="false">SUM(B36:U36)</f>
         <v>151022.7813056</v>
       </c>
-      <c r="S36" s="62" t="s">
-        <v>483</v>
+      <c r="W36" s="62" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B37" s="47" t="n">
         <f aca="false">B36-B16</f>
@@ -9150,72 +9455,88 @@
       </c>
       <c r="F37" s="47" t="n">
         <f aca="false">E37+F36-F16</f>
-        <v>0</v>
+        <v>32545.9792</v>
       </c>
       <c r="G37" s="47" t="n">
         <f aca="false">F37+G36-G16</f>
-        <v>29452.61584</v>
+        <v>61998.59504</v>
       </c>
       <c r="H37" s="47" t="n">
         <f aca="false">G37+H36-H16</f>
-        <v>0</v>
+        <v>61998.59504</v>
       </c>
       <c r="I37" s="47" t="n">
         <f aca="false">H37+I36-I16</f>
-        <v>29452.61584</v>
+        <v>91451.21088</v>
       </c>
       <c r="J37" s="47" t="n">
         <f aca="false">I37+J36-J16</f>
-        <v>0</v>
+        <v>91451.21088</v>
       </c>
       <c r="K37" s="47" t="n">
         <f aca="false">J37+K36-K16</f>
-        <v>29785.7852128</v>
+        <v>121236.9960928</v>
       </c>
       <c r="L37" s="47" t="n">
         <f aca="false">K37+L36-L16</f>
-        <v>0</v>
+        <v>121236.9960928</v>
       </c>
       <c r="M37" s="47" t="n">
         <f aca="false">L37+M36-M16</f>
-        <v>29785.7852128</v>
+        <v>118476.8021056</v>
       </c>
       <c r="N37" s="47" t="n">
         <f aca="false">M37+N36-N16</f>
-        <v>0</v>
+        <v>118476.8021056</v>
       </c>
       <c r="O37" s="47" t="n">
         <f aca="false">N37+O36-O16</f>
-        <v>0</v>
+        <v>89024.1862656</v>
       </c>
       <c r="P37" s="47" t="n">
         <f aca="false">O37+P36-P16</f>
-        <v>0</v>
+        <v>89024.1862656</v>
       </c>
       <c r="Q37" s="47" t="n">
         <f aca="false">P37+Q36-Q16</f>
-        <v>0</v>
-      </c>
-      <c r="R37" s="48"/>
+        <v>59571.5704256</v>
+      </c>
+      <c r="R37" s="47" t="n">
+        <f aca="false">Q37+R36-R16</f>
+        <v>59571.5704256</v>
+      </c>
+      <c r="S37" s="47" t="n">
+        <f aca="false">R37+S36-S16</f>
+        <v>29785.7852128</v>
+      </c>
+      <c r="T37" s="47" t="n">
+        <f aca="false">S37+T36-T16</f>
+        <v>29785.7852128</v>
+      </c>
+      <c r="U37" s="47" t="n">
+        <f aca="false">T37+U36-U16</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="48"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="36" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B40" s="63" t="n">
-        <f aca="false">MAX(B32:Q32)</f>
-        <v>37545.9252122344</v>
+        <f aca="false">MAX(B32:U32)</f>
+        <v>135206.941794999</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B41" s="63" t="n">
         <f aca="false">B8*Ressources!F8</f>
@@ -9224,37 +9545,37 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B42" s="58" t="str">
         <f aca="false">IF(B40&lt;=B41,"ok","DÉPASSEMENT")</f>
-        <v>ok</v>
+        <v>DÉPASSEMENT</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B43" s="63" t="n">
-        <f aca="false">SUM(B24:Q24)</f>
-        <v>3366.39158030878</v>
+        <f aca="false">SUM(B24:U24)</f>
+        <v>16115.9133825388</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B44" s="63" t="n">
         <f aca="false">Dépenses!F29</f>
-        <v>3366</v>
+        <v>16116</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B45" s="58" t="str">
         <f aca="false">IF(ABS(B43-B44)&lt;10,"ok","À METTRE À JOUR")</f>
@@ -9263,19 +9584,19 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B46" s="58" t="str">
-        <f aca="false">IF(Q32&lt;1,"ok","ENCOURS RESTANT")</f>
+        <f aca="false">IF(U32&lt;1,"ok","ENCOURS RESTANT")</f>
         <v>ok</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B47" s="58" t="str">
-        <f aca="false">IF(ABS(R17-Ressources!F17)&lt;1,"ok","ÉCART")</f>
+        <f aca="false">IF(ABS(V17-Ressources!F17)&lt;1,"ok","ÉCART")</f>
         <v>ok</v>
       </c>
     </row>
